--- a/template.xlsx
+++ b/template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\信息科技\Python\自创作品\课程表生成器\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\信息科技\Python\自创作品\课程表生成器\样例数据\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3B3C69C-B631-4391-BA52-A587D3D7E57D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61E63F43-2A4A-471D-9AAC-F4BCE048A74B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1552" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1550" uniqueCount="215">
   <si>
     <t>班级</t>
   </si>
@@ -673,16 +673,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>地理</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>阅读</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>本模板由AI生成，仅供测试使用，您可根据实际需求直接编辑该模板，内容如有雷同纯属巧合
-（编辑后请删除这句话）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -690,7 +681,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -700,14 +691,6 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="24"/>
-      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -734,9 +717,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1039,10 +1021,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AW53"/>
+  <dimension ref="A1:AU52"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1089,37 +1071,34 @@
         <v>10</v>
       </c>
       <c r="AD1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AF1" t="s">
         <v>11</v>
       </c>
       <c r="AH1" t="s">
-        <v>214</v>
+        <v>12</v>
       </c>
       <c r="AJ1" t="s">
-        <v>12</v>
+        <v>213</v>
       </c>
       <c r="AL1" t="s">
-        <v>213</v>
+        <v>13</v>
       </c>
       <c r="AN1" t="s">
-        <v>13</v>
+        <v>209</v>
       </c>
       <c r="AP1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AR1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AT1" t="s">
-        <v>211</v>
-      </c>
-      <c r="AV1" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -1183,26 +1162,26 @@
       <c r="AC2" t="s">
         <v>16</v>
       </c>
-      <c r="AP2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AQ2" t="s">
+      <c r="AN2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AO2" t="s">
         <v>28</v>
       </c>
+      <c r="AR2" t="s">
+        <v>21</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>18</v>
+      </c>
       <c r="AT2" t="s">
         <v>21</v>
       </c>
       <c r="AU2" t="s">
-        <v>18</v>
-      </c>
-      <c r="AV2" t="s">
-        <v>21</v>
-      </c>
-      <c r="AW2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -1266,26 +1245,26 @@
       <c r="AC3" t="s">
         <v>30</v>
       </c>
-      <c r="AP3" t="s">
-        <v>19</v>
-      </c>
-      <c r="AQ3" t="s">
+      <c r="AN3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AO3" t="s">
         <v>28</v>
       </c>
+      <c r="AR3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>31</v>
+      </c>
       <c r="AT3" t="s">
         <v>21</v>
       </c>
       <c r="AU3" t="s">
-        <v>31</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>21</v>
-      </c>
-      <c r="AW3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -1349,26 +1328,26 @@
       <c r="AC4" t="s">
         <v>34</v>
       </c>
-      <c r="AP4" t="s">
-        <v>19</v>
-      </c>
-      <c r="AQ4" t="s">
+      <c r="AN4" t="s">
+        <v>19</v>
+      </c>
+      <c r="AO4" t="s">
         <v>28</v>
       </c>
+      <c r="AR4" t="s">
+        <v>21</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>35</v>
+      </c>
       <c r="AT4" t="s">
         <v>21</v>
       </c>
       <c r="AU4" t="s">
-        <v>35</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>21</v>
-      </c>
-      <c r="AW4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>36</v>
       </c>
@@ -1432,26 +1411,26 @@
       <c r="AC5" t="s">
         <v>37</v>
       </c>
-      <c r="AP5" t="s">
-        <v>19</v>
-      </c>
-      <c r="AQ5" t="s">
+      <c r="AN5" t="s">
+        <v>19</v>
+      </c>
+      <c r="AO5" t="s">
         <v>28</v>
       </c>
+      <c r="AR5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>38</v>
+      </c>
       <c r="AT5" t="s">
         <v>21</v>
       </c>
       <c r="AU5" t="s">
-        <v>38</v>
-      </c>
-      <c r="AV5" t="s">
-        <v>21</v>
-      </c>
-      <c r="AW5" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>39</v>
       </c>
@@ -1515,26 +1494,26 @@
       <c r="AC6" t="s">
         <v>40</v>
       </c>
-      <c r="AP6" t="s">
-        <v>19</v>
-      </c>
-      <c r="AQ6" t="s">
+      <c r="AN6" t="s">
+        <v>19</v>
+      </c>
+      <c r="AO6" t="s">
         <v>28</v>
       </c>
+      <c r="AR6" t="s">
+        <v>21</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>31</v>
+      </c>
       <c r="AT6" t="s">
         <v>21</v>
       </c>
       <c r="AU6" t="s">
-        <v>31</v>
-      </c>
-      <c r="AV6" t="s">
-        <v>21</v>
-      </c>
-      <c r="AW6" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>42</v>
       </c>
@@ -1598,26 +1577,26 @@
       <c r="AC7" t="s">
         <v>43</v>
       </c>
-      <c r="AP7" t="s">
-        <v>19</v>
-      </c>
-      <c r="AQ7" t="s">
+      <c r="AN7" t="s">
+        <v>19</v>
+      </c>
+      <c r="AO7" t="s">
         <v>28</v>
       </c>
+      <c r="AR7" t="s">
+        <v>21</v>
+      </c>
+      <c r="AS7" t="s">
+        <v>44</v>
+      </c>
       <c r="AT7" t="s">
         <v>21</v>
       </c>
       <c r="AU7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AV7" t="s">
-        <v>21</v>
-      </c>
-      <c r="AW7" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>46</v>
       </c>
@@ -1681,26 +1660,26 @@
       <c r="AC8" t="s">
         <v>47</v>
       </c>
-      <c r="AP8" t="s">
-        <v>19</v>
-      </c>
-      <c r="AQ8" t="s">
+      <c r="AN8" t="s">
+        <v>19</v>
+      </c>
+      <c r="AO8" t="s">
         <v>28</v>
       </c>
+      <c r="AR8" t="s">
+        <v>21</v>
+      </c>
+      <c r="AS8" t="s">
+        <v>18</v>
+      </c>
       <c r="AT8" t="s">
         <v>21</v>
       </c>
       <c r="AU8" t="s">
-        <v>18</v>
-      </c>
-      <c r="AV8" t="s">
-        <v>21</v>
-      </c>
-      <c r="AW8" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>49</v>
       </c>
@@ -1764,26 +1743,26 @@
       <c r="AC9" t="s">
         <v>50</v>
       </c>
-      <c r="AP9" t="s">
-        <v>19</v>
-      </c>
-      <c r="AQ9" t="s">
+      <c r="AN9" t="s">
+        <v>19</v>
+      </c>
+      <c r="AO9" t="s">
         <v>28</v>
       </c>
+      <c r="AR9" t="s">
+        <v>21</v>
+      </c>
+      <c r="AS9" t="s">
+        <v>38</v>
+      </c>
       <c r="AT9" t="s">
         <v>21</v>
       </c>
       <c r="AU9" t="s">
-        <v>38</v>
-      </c>
-      <c r="AV9" t="s">
-        <v>21</v>
-      </c>
-      <c r="AW9" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>51</v>
       </c>
@@ -1847,26 +1826,26 @@
       <c r="AC10" t="s">
         <v>52</v>
       </c>
-      <c r="AP10" t="s">
-        <v>19</v>
-      </c>
-      <c r="AQ10" t="s">
+      <c r="AN10" t="s">
+        <v>19</v>
+      </c>
+      <c r="AO10" t="s">
         <v>28</v>
       </c>
+      <c r="AR10" t="s">
+        <v>21</v>
+      </c>
+      <c r="AS10" t="s">
+        <v>35</v>
+      </c>
       <c r="AT10" t="s">
         <v>21</v>
       </c>
       <c r="AU10" t="s">
-        <v>35</v>
-      </c>
-      <c r="AV10" t="s">
-        <v>21</v>
-      </c>
-      <c r="AW10" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>54</v>
       </c>
@@ -1930,26 +1909,26 @@
       <c r="AC11" t="s">
         <v>55</v>
       </c>
-      <c r="AP11" t="s">
-        <v>19</v>
-      </c>
-      <c r="AQ11" t="s">
+      <c r="AN11" t="s">
+        <v>19</v>
+      </c>
+      <c r="AO11" t="s">
         <v>57</v>
       </c>
+      <c r="AR11" t="s">
+        <v>21</v>
+      </c>
+      <c r="AS11" t="s">
+        <v>56</v>
+      </c>
       <c r="AT11" t="s">
         <v>21</v>
       </c>
       <c r="AU11" t="s">
-        <v>56</v>
-      </c>
-      <c r="AV11" t="s">
-        <v>21</v>
-      </c>
-      <c r="AW11" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="12" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>63</v>
       </c>
@@ -2013,26 +1992,26 @@
       <c r="AC12" t="s">
         <v>64</v>
       </c>
-      <c r="AP12" t="s">
-        <v>19</v>
-      </c>
-      <c r="AQ12" t="s">
+      <c r="AN12" t="s">
+        <v>19</v>
+      </c>
+      <c r="AO12" t="s">
         <v>57</v>
       </c>
+      <c r="AR12" t="s">
+        <v>21</v>
+      </c>
+      <c r="AS12" t="s">
+        <v>65</v>
+      </c>
       <c r="AT12" t="s">
         <v>21</v>
       </c>
       <c r="AU12" t="s">
-        <v>65</v>
-      </c>
-      <c r="AV12" t="s">
-        <v>21</v>
-      </c>
-      <c r="AW12" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="13" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>67</v>
       </c>
@@ -2096,26 +2075,26 @@
       <c r="AC13" t="s">
         <v>68</v>
       </c>
-      <c r="AP13" t="s">
-        <v>19</v>
-      </c>
-      <c r="AQ13" t="s">
+      <c r="AN13" t="s">
+        <v>19</v>
+      </c>
+      <c r="AO13" t="s">
         <v>20</v>
       </c>
+      <c r="AR13" t="s">
+        <v>21</v>
+      </c>
+      <c r="AS13" t="s">
+        <v>69</v>
+      </c>
       <c r="AT13" t="s">
         <v>21</v>
       </c>
       <c r="AU13" t="s">
-        <v>69</v>
-      </c>
-      <c r="AV13" t="s">
-        <v>21</v>
-      </c>
-      <c r="AW13" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>71</v>
       </c>
@@ -2179,26 +2158,26 @@
       <c r="AC14" t="s">
         <v>72</v>
       </c>
-      <c r="AP14" t="s">
-        <v>19</v>
-      </c>
-      <c r="AQ14" t="s">
+      <c r="AN14" t="s">
+        <v>19</v>
+      </c>
+      <c r="AO14" t="s">
         <v>74</v>
       </c>
+      <c r="AR14" t="s">
+        <v>21</v>
+      </c>
+      <c r="AS14" t="s">
+        <v>73</v>
+      </c>
       <c r="AT14" t="s">
         <v>21</v>
       </c>
       <c r="AU14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AV14" t="s">
-        <v>21</v>
-      </c>
-      <c r="AW14" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="15" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>77</v>
       </c>
@@ -2262,26 +2241,26 @@
       <c r="AC15" t="s">
         <v>78</v>
       </c>
-      <c r="AP15" t="s">
-        <v>19</v>
-      </c>
-      <c r="AQ15" t="s">
+      <c r="AN15" t="s">
+        <v>19</v>
+      </c>
+      <c r="AO15" t="s">
         <v>74</v>
       </c>
+      <c r="AR15" t="s">
+        <v>21</v>
+      </c>
+      <c r="AS15" t="s">
+        <v>69</v>
+      </c>
       <c r="AT15" t="s">
         <v>21</v>
       </c>
       <c r="AU15" t="s">
-        <v>69</v>
-      </c>
-      <c r="AV15" t="s">
-        <v>21</v>
-      </c>
-      <c r="AW15" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="16" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>80</v>
       </c>
@@ -2345,26 +2324,26 @@
       <c r="AC16" t="s">
         <v>81</v>
       </c>
-      <c r="AP16" t="s">
-        <v>19</v>
-      </c>
-      <c r="AQ16" t="s">
+      <c r="AN16" t="s">
+        <v>19</v>
+      </c>
+      <c r="AO16" t="s">
         <v>74</v>
       </c>
+      <c r="AR16" t="s">
+        <v>21</v>
+      </c>
+      <c r="AS16" t="s">
+        <v>82</v>
+      </c>
       <c r="AT16" t="s">
         <v>21</v>
       </c>
       <c r="AU16" t="s">
-        <v>82</v>
-      </c>
-      <c r="AV16" t="s">
-        <v>21</v>
-      </c>
-      <c r="AW16" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="17" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>84</v>
       </c>
@@ -2428,26 +2407,26 @@
       <c r="AC17" t="s">
         <v>56</v>
       </c>
-      <c r="AP17" t="s">
-        <v>19</v>
-      </c>
-      <c r="AQ17" t="s">
+      <c r="AN17" t="s">
+        <v>19</v>
+      </c>
+      <c r="AO17" t="s">
         <v>74</v>
       </c>
+      <c r="AR17" t="s">
+        <v>21</v>
+      </c>
+      <c r="AS17" t="s">
+        <v>56</v>
+      </c>
       <c r="AT17" t="s">
         <v>21</v>
       </c>
       <c r="AU17" t="s">
-        <v>56</v>
-      </c>
-      <c r="AV17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AW17" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="18" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>86</v>
       </c>
@@ -2511,26 +2490,26 @@
       <c r="AC18" t="s">
         <v>87</v>
       </c>
-      <c r="AP18" t="s">
-        <v>19</v>
-      </c>
-      <c r="AQ18" t="s">
+      <c r="AN18" t="s">
+        <v>19</v>
+      </c>
+      <c r="AO18" t="s">
         <v>57</v>
       </c>
+      <c r="AR18" t="s">
+        <v>21</v>
+      </c>
+      <c r="AS18" t="s">
+        <v>82</v>
+      </c>
       <c r="AT18" t="s">
         <v>21</v>
       </c>
       <c r="AU18" t="s">
-        <v>82</v>
-      </c>
-      <c r="AV18" t="s">
-        <v>21</v>
-      </c>
-      <c r="AW18" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="19" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>88</v>
       </c>
@@ -2594,26 +2573,26 @@
       <c r="AC19" t="s">
         <v>89</v>
       </c>
-      <c r="AP19" t="s">
-        <v>19</v>
-      </c>
-      <c r="AQ19" t="s">
+      <c r="AN19" t="s">
+        <v>19</v>
+      </c>
+      <c r="AO19" t="s">
         <v>20</v>
       </c>
+      <c r="AR19" t="s">
+        <v>21</v>
+      </c>
+      <c r="AS19" t="s">
+        <v>90</v>
+      </c>
       <c r="AT19" t="s">
         <v>21</v>
       </c>
       <c r="AU19" t="s">
-        <v>90</v>
-      </c>
-      <c r="AV19" t="s">
-        <v>21</v>
-      </c>
-      <c r="AW19" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="20" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>91</v>
       </c>
@@ -2677,26 +2656,26 @@
       <c r="AC20" t="s">
         <v>92</v>
       </c>
-      <c r="AP20" t="s">
-        <v>19</v>
-      </c>
-      <c r="AQ20" t="s">
+      <c r="AN20" t="s">
+        <v>19</v>
+      </c>
+      <c r="AO20" t="s">
         <v>57</v>
       </c>
+      <c r="AR20" t="s">
+        <v>21</v>
+      </c>
+      <c r="AS20" t="s">
+        <v>90</v>
+      </c>
       <c r="AT20" t="s">
         <v>21</v>
       </c>
       <c r="AU20" t="s">
-        <v>90</v>
-      </c>
-      <c r="AV20" t="s">
-        <v>21</v>
-      </c>
-      <c r="AW20" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="21" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>93</v>
       </c>
@@ -2760,26 +2739,26 @@
       <c r="AC21" t="s">
         <v>94</v>
       </c>
-      <c r="AP21" t="s">
-        <v>19</v>
-      </c>
-      <c r="AQ21" t="s">
+      <c r="AN21" t="s">
+        <v>19</v>
+      </c>
+      <c r="AO21" t="s">
         <v>20</v>
       </c>
+      <c r="AR21" t="s">
+        <v>21</v>
+      </c>
+      <c r="AS21" t="s">
+        <v>65</v>
+      </c>
       <c r="AT21" t="s">
         <v>21</v>
       </c>
       <c r="AU21" t="s">
-        <v>65</v>
-      </c>
-      <c r="AV21" t="s">
-        <v>21</v>
-      </c>
-      <c r="AW21" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="22" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>95</v>
       </c>
@@ -2861,20 +2840,20 @@
       <c r="AI22" t="s">
         <v>98</v>
       </c>
-      <c r="AN22" t="s">
-        <v>19</v>
-      </c>
-      <c r="AO22" t="s">
+      <c r="AL22" t="s">
+        <v>19</v>
+      </c>
+      <c r="AM22" t="s">
         <v>104</v>
       </c>
-      <c r="AR22" t="s">
-        <v>19</v>
-      </c>
-      <c r="AS22" t="s">
+      <c r="AP22" t="s">
+        <v>19</v>
+      </c>
+      <c r="AQ22" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="23" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>106</v>
       </c>
@@ -2956,20 +2935,20 @@
       <c r="AI23" t="s">
         <v>107</v>
       </c>
-      <c r="AN23" t="s">
-        <v>19</v>
-      </c>
-      <c r="AO23" t="s">
+      <c r="AL23" t="s">
+        <v>19</v>
+      </c>
+      <c r="AM23" t="s">
         <v>104</v>
       </c>
-      <c r="AR23" t="s">
-        <v>19</v>
-      </c>
-      <c r="AS23" t="s">
+      <c r="AP23" t="s">
+        <v>19</v>
+      </c>
+      <c r="AQ23" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="24" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>110</v>
       </c>
@@ -3051,20 +3030,20 @@
       <c r="AI24" t="s">
         <v>98</v>
       </c>
-      <c r="AN24" t="s">
-        <v>19</v>
-      </c>
-      <c r="AO24" t="s">
+      <c r="AL24" t="s">
+        <v>19</v>
+      </c>
+      <c r="AM24" t="s">
         <v>104</v>
       </c>
-      <c r="AR24" t="s">
-        <v>19</v>
-      </c>
-      <c r="AS24" t="s">
+      <c r="AP24" t="s">
+        <v>19</v>
+      </c>
+      <c r="AQ24" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="25" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>113</v>
       </c>
@@ -3146,20 +3125,20 @@
       <c r="AI25" t="s">
         <v>107</v>
       </c>
-      <c r="AN25" t="s">
-        <v>19</v>
-      </c>
-      <c r="AO25" t="s">
+      <c r="AL25" t="s">
+        <v>19</v>
+      </c>
+      <c r="AM25" t="s">
         <v>104</v>
       </c>
-      <c r="AR25" t="s">
-        <v>19</v>
-      </c>
-      <c r="AS25" t="s">
+      <c r="AP25" t="s">
+        <v>19</v>
+      </c>
+      <c r="AQ25" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="26" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>116</v>
       </c>
@@ -3241,20 +3220,20 @@
       <c r="AI26" t="s">
         <v>98</v>
       </c>
-      <c r="AN26" t="s">
-        <v>19</v>
-      </c>
-      <c r="AO26" t="s">
+      <c r="AL26" t="s">
+        <v>19</v>
+      </c>
+      <c r="AM26" t="s">
         <v>104</v>
       </c>
-      <c r="AR26" t="s">
-        <v>19</v>
-      </c>
-      <c r="AS26" t="s">
+      <c r="AP26" t="s">
+        <v>19</v>
+      </c>
+      <c r="AQ26" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="27" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>119</v>
       </c>
@@ -3336,20 +3315,20 @@
       <c r="AI27" t="s">
         <v>98</v>
       </c>
-      <c r="AN27" t="s">
-        <v>19</v>
-      </c>
-      <c r="AO27" t="s">
+      <c r="AL27" t="s">
+        <v>19</v>
+      </c>
+      <c r="AM27" t="s">
         <v>28</v>
       </c>
-      <c r="AR27" t="s">
-        <v>19</v>
-      </c>
-      <c r="AS27" t="s">
+      <c r="AP27" t="s">
+        <v>19</v>
+      </c>
+      <c r="AQ27" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="28" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>120</v>
       </c>
@@ -3431,20 +3410,20 @@
       <c r="AI28" t="s">
         <v>107</v>
       </c>
-      <c r="AN28" t="s">
-        <v>19</v>
-      </c>
-      <c r="AO28" t="s">
+      <c r="AL28" t="s">
+        <v>19</v>
+      </c>
+      <c r="AM28" t="s">
         <v>28</v>
       </c>
-      <c r="AR28" t="s">
-        <v>19</v>
-      </c>
-      <c r="AS28" t="s">
+      <c r="AP28" t="s">
+        <v>19</v>
+      </c>
+      <c r="AQ28" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="29" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>121</v>
       </c>
@@ -3526,26 +3505,26 @@
       <c r="AG29" t="s">
         <v>123</v>
       </c>
-      <c r="AJ29" t="s">
-        <v>19</v>
-      </c>
-      <c r="AK29" t="s">
+      <c r="AH29" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI29" t="s">
         <v>102</v>
       </c>
-      <c r="AN29" t="s">
-        <v>19</v>
-      </c>
-      <c r="AO29" t="s">
+      <c r="AL29" t="s">
+        <v>19</v>
+      </c>
+      <c r="AM29" t="s">
         <v>104</v>
       </c>
-      <c r="AR29" t="s">
-        <v>19</v>
-      </c>
-      <c r="AS29" t="s">
+      <c r="AP29" t="s">
+        <v>19</v>
+      </c>
+      <c r="AQ29" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="30" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>130</v>
       </c>
@@ -3627,26 +3606,26 @@
       <c r="AG30" t="s">
         <v>132</v>
       </c>
-      <c r="AJ30" t="s">
-        <v>19</v>
-      </c>
-      <c r="AK30" t="s">
+      <c r="AH30" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI30" t="s">
         <v>117</v>
       </c>
-      <c r="AN30" t="s">
-        <v>19</v>
-      </c>
-      <c r="AO30" t="s">
+      <c r="AL30" t="s">
+        <v>19</v>
+      </c>
+      <c r="AM30" t="s">
         <v>104</v>
       </c>
-      <c r="AR30" t="s">
-        <v>19</v>
-      </c>
-      <c r="AS30" t="s">
+      <c r="AP30" t="s">
+        <v>19</v>
+      </c>
+      <c r="AQ30" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="31" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>134</v>
       </c>
@@ -3728,26 +3707,26 @@
       <c r="AG31" t="s">
         <v>123</v>
       </c>
-      <c r="AJ31" t="s">
-        <v>19</v>
-      </c>
-      <c r="AK31" t="s">
+      <c r="AH31" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI31" t="s">
         <v>102</v>
       </c>
-      <c r="AN31" t="s">
-        <v>19</v>
-      </c>
-      <c r="AO31" t="s">
+      <c r="AL31" t="s">
+        <v>19</v>
+      </c>
+      <c r="AM31" t="s">
         <v>104</v>
       </c>
-      <c r="AR31" t="s">
-        <v>19</v>
-      </c>
-      <c r="AS31" t="s">
+      <c r="AP31" t="s">
+        <v>19</v>
+      </c>
+      <c r="AQ31" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="32" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>139</v>
       </c>
@@ -3829,26 +3808,26 @@
       <c r="AG32" t="s">
         <v>132</v>
       </c>
-      <c r="AJ32" t="s">
-        <v>19</v>
-      </c>
-      <c r="AK32" t="s">
+      <c r="AH32" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI32" t="s">
         <v>102</v>
       </c>
-      <c r="AN32" t="s">
-        <v>19</v>
-      </c>
-      <c r="AO32" t="s">
+      <c r="AL32" t="s">
+        <v>19</v>
+      </c>
+      <c r="AM32" t="s">
         <v>104</v>
       </c>
-      <c r="AR32" t="s">
-        <v>19</v>
-      </c>
-      <c r="AS32" t="s">
+      <c r="AP32" t="s">
+        <v>19</v>
+      </c>
+      <c r="AQ32" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="33" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>142</v>
       </c>
@@ -3930,26 +3909,26 @@
       <c r="AG33" t="s">
         <v>146</v>
       </c>
-      <c r="AJ33" t="s">
-        <v>19</v>
-      </c>
-      <c r="AK33" t="s">
+      <c r="AH33" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI33" t="s">
         <v>117</v>
       </c>
-      <c r="AN33" t="s">
-        <v>19</v>
-      </c>
-      <c r="AO33" t="s">
+      <c r="AL33" t="s">
+        <v>19</v>
+      </c>
+      <c r="AM33" t="s">
         <v>28</v>
       </c>
-      <c r="AR33" t="s">
-        <v>19</v>
-      </c>
-      <c r="AS33" t="s">
+      <c r="AP33" t="s">
+        <v>19</v>
+      </c>
+      <c r="AQ33" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="34" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>147</v>
       </c>
@@ -4031,26 +4010,26 @@
       <c r="AG34" t="s">
         <v>146</v>
       </c>
-      <c r="AJ34" t="s">
-        <v>19</v>
-      </c>
-      <c r="AK34" t="s">
+      <c r="AH34" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI34" t="s">
         <v>102</v>
       </c>
-      <c r="AN34" t="s">
-        <v>19</v>
-      </c>
-      <c r="AO34" t="s">
+      <c r="AL34" t="s">
+        <v>19</v>
+      </c>
+      <c r="AM34" t="s">
         <v>104</v>
       </c>
-      <c r="AR34" t="s">
-        <v>19</v>
-      </c>
-      <c r="AS34" t="s">
+      <c r="AP34" t="s">
+        <v>19</v>
+      </c>
+      <c r="AQ34" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="35" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>150</v>
       </c>
@@ -4132,26 +4111,26 @@
       <c r="AG35" t="s">
         <v>146</v>
       </c>
-      <c r="AJ35" t="s">
-        <v>19</v>
-      </c>
-      <c r="AK35" t="s">
+      <c r="AH35" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI35" t="s">
         <v>117</v>
       </c>
-      <c r="AN35" t="s">
-        <v>19</v>
-      </c>
-      <c r="AO35" t="s">
+      <c r="AL35" t="s">
+        <v>19</v>
+      </c>
+      <c r="AM35" t="s">
         <v>104</v>
       </c>
-      <c r="AR35" t="s">
-        <v>19</v>
-      </c>
-      <c r="AS35" t="s">
+      <c r="AP35" t="s">
+        <v>19</v>
+      </c>
+      <c r="AQ35" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="36" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>152</v>
       </c>
@@ -4233,26 +4212,26 @@
       <c r="AG36" t="s">
         <v>123</v>
       </c>
-      <c r="AJ36" t="s">
-        <v>19</v>
-      </c>
-      <c r="AK36" t="s">
+      <c r="AH36" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI36" t="s">
         <v>117</v>
       </c>
-      <c r="AN36" t="s">
-        <v>19</v>
-      </c>
-      <c r="AO36" t="s">
+      <c r="AL36" t="s">
+        <v>19</v>
+      </c>
+      <c r="AM36" t="s">
         <v>104</v>
       </c>
-      <c r="AR36" t="s">
-        <v>19</v>
-      </c>
-      <c r="AS36" t="s">
+      <c r="AP36" t="s">
+        <v>19</v>
+      </c>
+      <c r="AQ36" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="37" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>153</v>
       </c>
@@ -4334,26 +4313,26 @@
       <c r="AG37" t="s">
         <v>156</v>
       </c>
-      <c r="AJ37" t="s">
-        <v>19</v>
-      </c>
-      <c r="AK37" t="s">
+      <c r="AH37" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI37" t="s">
         <v>160</v>
       </c>
-      <c r="AN37" t="s">
-        <v>19</v>
-      </c>
-      <c r="AO37" t="s">
+      <c r="AL37" t="s">
+        <v>19</v>
+      </c>
+      <c r="AM37" t="s">
         <v>104</v>
       </c>
-      <c r="AR37" t="s">
-        <v>19</v>
-      </c>
-      <c r="AS37" t="s">
+      <c r="AP37" t="s">
+        <v>19</v>
+      </c>
+      <c r="AQ37" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="38" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>161</v>
       </c>
@@ -4435,26 +4414,26 @@
       <c r="AG38" t="s">
         <v>132</v>
       </c>
-      <c r="AJ38" t="s">
-        <v>19</v>
-      </c>
-      <c r="AK38" t="s">
+      <c r="AH38" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI38" t="s">
         <v>160</v>
       </c>
-      <c r="AN38" t="s">
-        <v>19</v>
-      </c>
-      <c r="AO38" t="s">
+      <c r="AL38" t="s">
+        <v>19</v>
+      </c>
+      <c r="AM38" t="s">
         <v>104</v>
       </c>
-      <c r="AR38" t="s">
-        <v>19</v>
-      </c>
-      <c r="AS38" t="s">
+      <c r="AP38" t="s">
+        <v>19</v>
+      </c>
+      <c r="AQ38" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="39" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>166</v>
       </c>
@@ -4536,26 +4515,26 @@
       <c r="AG39" t="s">
         <v>167</v>
       </c>
-      <c r="AJ39" t="s">
-        <v>19</v>
-      </c>
-      <c r="AK39" t="s">
+      <c r="AH39" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI39" t="s">
         <v>160</v>
       </c>
-      <c r="AN39" t="s">
-        <v>19</v>
-      </c>
-      <c r="AO39" t="s">
+      <c r="AL39" t="s">
+        <v>19</v>
+      </c>
+      <c r="AM39" t="s">
         <v>28</v>
       </c>
-      <c r="AR39" t="s">
-        <v>19</v>
-      </c>
-      <c r="AS39" t="s">
+      <c r="AP39" t="s">
+        <v>19</v>
+      </c>
+      <c r="AQ39" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="40" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>170</v>
       </c>
@@ -4637,26 +4616,26 @@
       <c r="AG40" t="s">
         <v>163</v>
       </c>
-      <c r="AJ40" t="s">
-        <v>19</v>
-      </c>
-      <c r="AK40" t="s">
+      <c r="AH40" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI40" t="s">
         <v>160</v>
       </c>
-      <c r="AN40" t="s">
-        <v>19</v>
-      </c>
-      <c r="AO40" t="s">
+      <c r="AL40" t="s">
+        <v>19</v>
+      </c>
+      <c r="AM40" t="s">
         <v>104</v>
       </c>
-      <c r="AR40" t="s">
-        <v>19</v>
-      </c>
-      <c r="AS40" t="s">
+      <c r="AP40" t="s">
+        <v>19</v>
+      </c>
+      <c r="AQ40" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="41" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>172</v>
       </c>
@@ -4738,26 +4717,26 @@
       <c r="AG41" t="s">
         <v>167</v>
       </c>
-      <c r="AJ41" t="s">
-        <v>19</v>
-      </c>
-      <c r="AK41" t="s">
+      <c r="AH41" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI41" t="s">
         <v>175</v>
       </c>
-      <c r="AN41" t="s">
-        <v>19</v>
-      </c>
-      <c r="AO41" t="s">
+      <c r="AL41" t="s">
+        <v>19</v>
+      </c>
+      <c r="AM41" t="s">
         <v>104</v>
       </c>
-      <c r="AR41" t="s">
-        <v>19</v>
-      </c>
-      <c r="AS41" t="s">
+      <c r="AP41" t="s">
+        <v>19</v>
+      </c>
+      <c r="AQ41" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="42" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>177</v>
       </c>
@@ -4839,26 +4818,26 @@
       <c r="AG42" t="s">
         <v>132</v>
       </c>
-      <c r="AJ42" t="s">
-        <v>19</v>
-      </c>
-      <c r="AK42" t="s">
+      <c r="AH42" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI42" t="s">
         <v>175</v>
       </c>
-      <c r="AN42" t="s">
-        <v>19</v>
-      </c>
-      <c r="AO42" t="s">
+      <c r="AL42" t="s">
+        <v>19</v>
+      </c>
+      <c r="AM42" t="s">
         <v>104</v>
       </c>
-      <c r="AR42" t="s">
-        <v>19</v>
-      </c>
-      <c r="AS42" t="s">
+      <c r="AP42" t="s">
+        <v>19</v>
+      </c>
+      <c r="AQ42" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="43" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>179</v>
       </c>
@@ -4940,26 +4919,26 @@
       <c r="AG43" t="s">
         <v>180</v>
       </c>
-      <c r="AJ43" t="s">
-        <v>19</v>
-      </c>
-      <c r="AK43" t="s">
+      <c r="AH43" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI43" t="s">
         <v>175</v>
       </c>
-      <c r="AN43" t="s">
-        <v>19</v>
-      </c>
-      <c r="AO43" t="s">
+      <c r="AL43" t="s">
+        <v>19</v>
+      </c>
+      <c r="AM43" t="s">
         <v>104</v>
       </c>
-      <c r="AR43" t="s">
-        <v>19</v>
-      </c>
-      <c r="AS43" t="s">
+      <c r="AP43" t="s">
+        <v>19</v>
+      </c>
+      <c r="AQ43" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="44" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>181</v>
       </c>
@@ -5041,26 +5020,26 @@
       <c r="AG44" t="s">
         <v>180</v>
       </c>
-      <c r="AJ44" t="s">
-        <v>19</v>
-      </c>
-      <c r="AK44" t="s">
+      <c r="AH44" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI44" t="s">
         <v>175</v>
       </c>
-      <c r="AN44" t="s">
-        <v>19</v>
-      </c>
-      <c r="AO44" t="s">
+      <c r="AL44" t="s">
+        <v>19</v>
+      </c>
+      <c r="AM44" t="s">
         <v>104</v>
       </c>
-      <c r="AR44" t="s">
-        <v>19</v>
-      </c>
-      <c r="AS44" t="s">
+      <c r="AP44" t="s">
+        <v>19</v>
+      </c>
+      <c r="AQ44" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="45" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>182</v>
       </c>
@@ -5136,26 +5115,26 @@
       <c r="AG45" t="s">
         <v>184</v>
       </c>
+      <c r="AJ45" t="s">
+        <v>19</v>
+      </c>
+      <c r="AK45" t="s">
+        <v>44</v>
+      </c>
       <c r="AL45" t="s">
         <v>19</v>
       </c>
       <c r="AM45" t="s">
-        <v>44</v>
-      </c>
-      <c r="AN45" t="s">
-        <v>19</v>
-      </c>
-      <c r="AO45" t="s">
         <v>104</v>
       </c>
-      <c r="AR45" t="s">
-        <v>19</v>
-      </c>
-      <c r="AS45" t="s">
+      <c r="AP45" t="s">
+        <v>19</v>
+      </c>
+      <c r="AQ45" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="46" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>188</v>
       </c>
@@ -5231,26 +5210,26 @@
       <c r="AG46" t="s">
         <v>189</v>
       </c>
+      <c r="AJ46" t="s">
+        <v>19</v>
+      </c>
+      <c r="AK46" t="s">
+        <v>187</v>
+      </c>
       <c r="AL46" t="s">
         <v>19</v>
       </c>
       <c r="AM46" t="s">
+        <v>28</v>
+      </c>
+      <c r="AP46" t="s">
+        <v>19</v>
+      </c>
+      <c r="AQ46" t="s">
         <v>187</v>
       </c>
-      <c r="AN46" t="s">
-        <v>19</v>
-      </c>
-      <c r="AO46" t="s">
-        <v>28</v>
-      </c>
-      <c r="AR46" t="s">
-        <v>19</v>
-      </c>
-      <c r="AS46" t="s">
-        <v>187</v>
-      </c>
     </row>
-    <row r="47" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>190</v>
       </c>
@@ -5326,26 +5305,26 @@
       <c r="AG47" t="s">
         <v>192</v>
       </c>
+      <c r="AJ47" t="s">
+        <v>19</v>
+      </c>
+      <c r="AK47" t="s">
+        <v>44</v>
+      </c>
       <c r="AL47" t="s">
         <v>19</v>
       </c>
       <c r="AM47" t="s">
-        <v>44</v>
-      </c>
-      <c r="AN47" t="s">
-        <v>19</v>
-      </c>
-      <c r="AO47" t="s">
         <v>104</v>
       </c>
-      <c r="AR47" t="s">
-        <v>19</v>
-      </c>
-      <c r="AS47" t="s">
+      <c r="AP47" t="s">
+        <v>19</v>
+      </c>
+      <c r="AQ47" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="48" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>193</v>
       </c>
@@ -5421,26 +5400,26 @@
       <c r="AG48" t="s">
         <v>192</v>
       </c>
+      <c r="AJ48" t="s">
+        <v>19</v>
+      </c>
+      <c r="AK48" t="s">
+        <v>44</v>
+      </c>
       <c r="AL48" t="s">
         <v>19</v>
       </c>
       <c r="AM48" t="s">
-        <v>44</v>
-      </c>
-      <c r="AN48" t="s">
-        <v>19</v>
-      </c>
-      <c r="AO48" t="s">
         <v>104</v>
       </c>
-      <c r="AR48" t="s">
-        <v>19</v>
-      </c>
-      <c r="AS48" t="s">
+      <c r="AP48" t="s">
+        <v>19</v>
+      </c>
+      <c r="AQ48" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="49" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>195</v>
       </c>
@@ -5516,26 +5495,26 @@
       <c r="AG49" t="s">
         <v>197</v>
       </c>
+      <c r="AJ49" t="s">
+        <v>19</v>
+      </c>
+      <c r="AK49" t="s">
+        <v>44</v>
+      </c>
       <c r="AL49" t="s">
         <v>19</v>
       </c>
       <c r="AM49" t="s">
-        <v>44</v>
-      </c>
-      <c r="AN49" t="s">
-        <v>19</v>
-      </c>
-      <c r="AO49" t="s">
         <v>104</v>
       </c>
-      <c r="AR49" t="s">
-        <v>19</v>
-      </c>
-      <c r="AS49" t="s">
+      <c r="AP49" t="s">
+        <v>19</v>
+      </c>
+      <c r="AQ49" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="50" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>199</v>
       </c>
@@ -5611,26 +5590,26 @@
       <c r="AG50" t="s">
         <v>184</v>
       </c>
+      <c r="AJ50" t="s">
+        <v>19</v>
+      </c>
+      <c r="AK50" t="s">
+        <v>44</v>
+      </c>
       <c r="AL50" t="s">
         <v>19</v>
       </c>
       <c r="AM50" t="s">
-        <v>44</v>
-      </c>
-      <c r="AN50" t="s">
-        <v>19</v>
-      </c>
-      <c r="AO50" t="s">
         <v>104</v>
       </c>
-      <c r="AR50" t="s">
-        <v>19</v>
-      </c>
-      <c r="AS50" t="s">
+      <c r="AP50" t="s">
+        <v>19</v>
+      </c>
+      <c r="AQ50" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="51" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>201</v>
       </c>
@@ -5706,26 +5685,26 @@
       <c r="AG51" t="s">
         <v>197</v>
       </c>
+      <c r="AJ51" t="s">
+        <v>19</v>
+      </c>
+      <c r="AK51" t="s">
+        <v>202</v>
+      </c>
       <c r="AL51" t="s">
         <v>19</v>
       </c>
       <c r="AM51" t="s">
-        <v>202</v>
-      </c>
-      <c r="AN51" t="s">
-        <v>19</v>
-      </c>
-      <c r="AO51" t="s">
         <v>28</v>
       </c>
-      <c r="AR51" t="s">
-        <v>19</v>
-      </c>
-      <c r="AS51" t="s">
+      <c r="AP51" t="s">
+        <v>19</v>
+      </c>
+      <c r="AQ51" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="52" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>203</v>
       </c>
@@ -5801,28 +5780,23 @@
       <c r="AG52" t="s">
         <v>189</v>
       </c>
+      <c r="AJ52" t="s">
+        <v>19</v>
+      </c>
+      <c r="AK52" t="s">
+        <v>204</v>
+      </c>
       <c r="AL52" t="s">
         <v>19</v>
       </c>
       <c r="AM52" t="s">
-        <v>204</v>
-      </c>
-      <c r="AN52" t="s">
-        <v>19</v>
-      </c>
-      <c r="AO52" t="s">
         <v>104</v>
       </c>
-      <c r="AR52" t="s">
-        <v>19</v>
-      </c>
-      <c r="AS52" t="s">
+      <c r="AP52" t="s">
+        <v>19</v>
+      </c>
+      <c r="AQ52" t="s">
         <v>136</v>
-      </c>
-    </row>
-    <row r="53" spans="1:45" ht="45.75" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A53" s="1" t="s">
-        <v>216</v>
       </c>
     </row>
   </sheetData>
